--- a/data_lake/industry/TrendForce/DRAM.xlsx
+++ b/data_lake/industry/TrendForce/DRAM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A412D9-38EC-4B8E-B1C7-5ADD83EEDFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8792952-9084-422F-AD02-BECA03CFA711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="61">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1456,6 +1456,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2427,6 +2436,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>46.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>46.633000000000003</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>46.633000000000003</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46.633000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3439,6 +3457,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4410,6 +4437,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>23.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5422,6 +5458,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6393,6 +6438,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>76.375</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>76.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7405,6 +7459,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8376,6 +8439,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>11.525</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>11.525</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9388,6 +9460,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10359,6 +10440,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>36.340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>36.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11387,6 +11477,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12358,6 +12457,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>4.2039999999999997</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4.2039999999999997</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4.1710000000000003</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4.1710000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13372,6 +13480,15 @@
                 <c:pt idx="321">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="322">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14343,6 +14460,15 @@
                 </c:pt>
                 <c:pt idx="320">
                   <c:v>12.340999999999999</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>12.340999999999999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>12.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>12.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18437,7 +18563,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z324"/>
+  <dimension ref="A1:Z327"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -43618,6 +43744,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D324" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E324" s="11">
+        <v>61</v>
+      </c>
+      <c r="F324" s="11">
+        <v>31</v>
+      </c>
+      <c r="G324" s="11">
+        <v>46.633000000000003</v>
+      </c>
+      <c r="H324" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I324" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J324" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K324" s="11">
+        <v>94</v>
+      </c>
+      <c r="L324" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M324" s="11">
+        <v>75.5</v>
+      </c>
+      <c r="N324" s="11">
+        <v>12</v>
+      </c>
+      <c r="O324" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P324" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="Q324" s="11">
+        <v>59</v>
+      </c>
+      <c r="R324" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S324" s="11">
+        <v>36.340000000000003</v>
+      </c>
+      <c r="T324" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U324" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V324" s="11">
+        <v>4.2039999999999997</v>
+      </c>
+      <c r="W324" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="X324" s="11">
+        <v>8</v>
+      </c>
+      <c r="Y324" s="11">
+        <v>12.340999999999999</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25">
+      <c r="A325" s="8">
+        <v>46206</v>
+      </c>
+      <c r="B325" s="8">
+        <v>46206</v>
+      </c>
+      <c r="C325" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D325" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E325" s="11">
+        <v>61</v>
+      </c>
+      <c r="F325" s="11">
+        <v>31</v>
+      </c>
+      <c r="G325" s="11">
+        <v>46.633000000000003</v>
+      </c>
+      <c r="H325" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I325" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J325" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="K325" s="11">
+        <v>95</v>
+      </c>
+      <c r="L325" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M325" s="11">
+        <v>76.375</v>
+      </c>
+      <c r="N325" s="11">
+        <v>12</v>
+      </c>
+      <c r="O325" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P325" s="11">
+        <v>11.525</v>
+      </c>
+      <c r="Q325" s="11">
+        <v>60</v>
+      </c>
+      <c r="R325" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S325" s="11">
+        <v>36.54</v>
+      </c>
+      <c r="T325" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U325" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V325" s="11">
+        <v>4.1710000000000003</v>
+      </c>
+      <c r="W325" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="X325" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Y325" s="11">
+        <v>12.476000000000001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25">
+      <c r="A326" s="8">
+        <v>46206</v>
+      </c>
+      <c r="B326" s="8">
+        <v>46206</v>
+      </c>
+      <c r="C326" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D326" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E326" s="11">
+        <v>61</v>
+      </c>
+      <c r="F326" s="11">
+        <v>31</v>
+      </c>
+      <c r="G326" s="11">
+        <v>46.633000000000003</v>
+      </c>
+      <c r="H326" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I326" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J326" s="11">
+        <v>23.25</v>
+      </c>
+      <c r="K326" s="11">
+        <v>95</v>
+      </c>
+      <c r="L326" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M326" s="11">
+        <v>76.375</v>
+      </c>
+      <c r="N326" s="11">
+        <v>12</v>
+      </c>
+      <c r="O326" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P326" s="11">
+        <v>11.525</v>
+      </c>
+      <c r="Q326" s="11">
+        <v>60</v>
+      </c>
+      <c r="R326" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S326" s="11">
+        <v>36.54</v>
+      </c>
+      <c r="T326" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U326" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V326" s="11">
+        <v>4.1710000000000003</v>
+      </c>
+      <c r="W326" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="X326" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Y326" s="11">
+        <v>12.476000000000001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25">
+      <c r="A327" s="8">
+        <v>46206</v>
+      </c>
+      <c r="B327" s="8">
+        <v>46206</v>
+      </c>
+      <c r="C327" s="9">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D327" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -43637,7 +43994,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -44266,6 +44623,83 @@
       </c>
       <c r="Y8" s="11">
         <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" s="8">
+        <v>46143</v>
+      </c>
+      <c r="B9" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="11">
+        <v>123</v>
+      </c>
+      <c r="F9" s="11">
+        <v>99</v>
+      </c>
+      <c r="G9" s="11">
+        <v>112</v>
+      </c>
+      <c r="H9" s="11">
+        <v>256</v>
+      </c>
+      <c r="I9" s="11">
+        <v>192</v>
+      </c>
+      <c r="J9" s="11">
+        <v>227</v>
+      </c>
+      <c r="K9" s="11">
+        <v>128</v>
+      </c>
+      <c r="L9" s="11">
+        <v>96</v>
+      </c>
+      <c r="M9" s="11">
+        <v>119</v>
+      </c>
+      <c r="N9" s="11">
+        <v>49</v>
+      </c>
+      <c r="O9" s="11">
+        <v>37</v>
+      </c>
+      <c r="P9" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>28</v>
+      </c>
+      <c r="R9" s="11">
+        <v>18</v>
+      </c>
+      <c r="S9" s="11">
+        <v>20</v>
+      </c>
+      <c r="T9" s="11">
+        <v>14</v>
+      </c>
+      <c r="U9" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="V9" s="11">
+        <v>12</v>
+      </c>
+      <c r="W9" s="11">
+        <v>14</v>
+      </c>
+      <c r="X9" s="11">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/DRAM.xlsx
+++ b/data_lake/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8792952-9084-422F-AD02-BECA03CFA711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50107733-0FD8-9440-B68D-3E13389B5F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -417,10 +417,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,7 +438,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2446,6 +2446,9 @@
                 <c:pt idx="323">
                   <c:v>46.633000000000003</c:v>
                 </c:pt>
+                <c:pt idx="324">
+                  <c:v>46.667000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4447,6 +4450,9 @@
                 <c:pt idx="323">
                   <c:v>23.25</c:v>
                 </c:pt>
+                <c:pt idx="324">
+                  <c:v>23.25</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6448,6 +6454,9 @@
                 <c:pt idx="323">
                   <c:v>76.375</c:v>
                 </c:pt>
+                <c:pt idx="324">
+                  <c:v>76.375</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8449,6 +8458,9 @@
                 <c:pt idx="323">
                   <c:v>11.525</c:v>
                 </c:pt>
+                <c:pt idx="324">
+                  <c:v>11.525</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10448,6 +10460,9 @@
                   <c:v>36.54</c:v>
                 </c:pt>
                 <c:pt idx="323">
+                  <c:v>36.54</c:v>
+                </c:pt>
+                <c:pt idx="324">
                   <c:v>36.54</c:v>
                 </c:pt>
               </c:numCache>
@@ -12467,6 +12482,9 @@
                 <c:pt idx="323">
                   <c:v>4.1710000000000003</c:v>
                 </c:pt>
+                <c:pt idx="324">
+                  <c:v>4.1710000000000003</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14468,6 +14486,9 @@
                   <c:v>12.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="323">
+                  <c:v>12.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="324">
                   <c:v>12.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -14747,7 +14768,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15786,7 +15807,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18564,14 +18585,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Z327"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="13" width="9" style="11"/>
-    <col min="14" max="14" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -43976,6 +43997,69 @@
       </c>
       <c r="D327" s="10" t="s">
         <v>53</v>
+      </c>
+      <c r="E327" s="11">
+        <v>61</v>
+      </c>
+      <c r="F327" s="11">
+        <v>31</v>
+      </c>
+      <c r="G327" s="11">
+        <v>46.667000000000002</v>
+      </c>
+      <c r="H327" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="I327" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="J327" s="11">
+        <v>23.25</v>
+      </c>
+      <c r="K327" s="11">
+        <v>95</v>
+      </c>
+      <c r="L327" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M327" s="11">
+        <v>76.375</v>
+      </c>
+      <c r="N327" s="11">
+        <v>12</v>
+      </c>
+      <c r="O327" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="P327" s="11">
+        <v>11.525</v>
+      </c>
+      <c r="Q327" s="11">
+        <v>60</v>
+      </c>
+      <c r="R327" s="11">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="S327" s="11">
+        <v>36.54</v>
+      </c>
+      <c r="T327" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U327" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="V327" s="11">
+        <v>4.1710000000000003</v>
+      </c>
+      <c r="W327" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="X327" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Y327" s="11">
+        <v>12.476000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -43995,21 +44079,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="11"/>
-    <col min="13" max="13" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -44718,17 +44802,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="9.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="15"/>
-    <col min="10" max="10" width="11.77734375" style="17" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="17" customWidth="1"/>
     <col min="11" max="12" width="9" style="15"/>
     <col min="13" max="13" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
@@ -46395,13 +46479,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -47759,7 +47843,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47772,11 +47856,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
